--- a/static/templates/import_education_docs.xlsx
+++ b/static/templates/import_education_docs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LocalAdm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC295B32-1D78-487F-9ECE-F3E049FCBDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59902412-BC9E-46C2-AE78-4576BCE67D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4710" yWindow="4170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="345" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Документи" sheetId="1" r:id="rId1"/>
@@ -25,67 +25,94 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
-  <si>
-    <t>Здобувач</t>
-  </si>
-  <si>
-    <t>Документ</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>Коваленко Марія Петрівна</t>
+  </si>
+  <si>
+    <t>Атестат про повну загальну середню освіту  БК 40920464; 15.06.2021; Ким видано: Ліцей №5 м. Одеса</t>
+  </si>
+  <si>
+    <t>Бондаренко Олег Васильович</t>
+  </si>
+  <si>
+    <t>Диплом молодшого спеціаліста  КМ 12345678; 30.06.2022; Ким видано: Київський коледж будівництва</t>
+  </si>
+  <si>
+    <t>Мельник Оксана Миколаївна</t>
+  </si>
+  <si>
+    <t>Диплом бакалавра  ВО 99887766; 25.06.2023; Ким видано: Львівський національний університет імені Івана Франка</t>
+  </si>
+  <si>
+    <t>Ткаченко Василь Іванович</t>
+  </si>
+  <si>
+    <t>Диплом бакалавра B24 001122; 10.06.2024; Харківський університет</t>
+  </si>
+  <si>
+    <t>Петренко Анна Сергіївна</t>
+  </si>
+  <si>
+    <t>Атестат НА 123456 20.06.2021 Ким видано: Школа №10</t>
+  </si>
+  <si>
+    <t>Іваненко Дмитро Олегович</t>
+  </si>
+  <si>
+    <t>Неіснуючий Студент Повністю</t>
+  </si>
+  <si>
+    <t>Диплом бакалавра  АА 000000; 01.01.2020; Ким видано: Якийсь університет</t>
+  </si>
+  <si>
+    <t>Савченко Юлія Андріївна</t>
+  </si>
+  <si>
+    <t>Диплом бакалавра  PL 556677; 15.07.2023; Ким видано: Університет Варшави, Польща</t>
+  </si>
+  <si>
+    <t>Мельник Денис Богданович</t>
+  </si>
+  <si>
+    <t>ПІБ студента</t>
+  </si>
+  <si>
+    <t>Рядок документа</t>
+  </si>
+  <si>
+    <t>Академічна довідка (укр)</t>
+  </si>
+  <si>
+    <t>Академічна довідка (en)</t>
+  </si>
+  <si>
+    <t>Свідоцтво про визнання (укр)</t>
+  </si>
+  <si>
+    <t>Свідоцтво про визнання (en)</t>
+  </si>
+  <si>
+    <t>№ N-7916-20; Private HEI "European University"; 12.05.2020</t>
+  </si>
+  <si>
+    <t>08-17/04; ТОВ Кавказький університет; Грузія; 02/06/2017</t>
+  </si>
+  <si>
+    <t>08-17/04; Caucasus University LLC; Georgia; 02/06/2017</t>
+  </si>
+  <si>
+    <t>№ N-7916-20; Приватний ВНЗ «Європейський університет»; 12/05/2020</t>
   </si>
   <si>
     <t>Диплом бакалавра  B24 088726; 20.06.2024; Ким видано: Харківський національний університет імені В.Н. Каразіна</t>
-  </si>
-  <si>
-    <t>Коваленко Марія Петрівна</t>
-  </si>
-  <si>
-    <t>Атестат про повну загальну середню освіту  БК 40920464; 15.06.2021; Ким видано: Ліцей №5 м. Одеса</t>
-  </si>
-  <si>
-    <t>Бондаренко Олег Васильович</t>
-  </si>
-  <si>
-    <t>Диплом молодшого спеціаліста  КМ 12345678; 30.06.2022; Ким видано: Київський коледж будівництва</t>
-  </si>
-  <si>
-    <t>Мельник Оксана Миколаївна</t>
-  </si>
-  <si>
-    <t>Диплом бакалавра  ВО 99887766; 25.06.2023; Ким видано: Львівський національний університет імені Івана Франка</t>
-  </si>
-  <si>
-    <t>Ткаченко Василь Іванович</t>
-  </si>
-  <si>
-    <t>Диплом бакалавра B24 001122; 10.06.2024; Харківський університет</t>
-  </si>
-  <si>
-    <t>Петренко Анна Сергіївна</t>
-  </si>
-  <si>
-    <t>Атестат НА 123456 20.06.2021 Ким видано: Школа №10</t>
-  </si>
-  <si>
-    <t>Іваненко Дмитро Олегович</t>
-  </si>
-  <si>
-    <t>Неіснуючий Студент Повністю</t>
-  </si>
-  <si>
-    <t>Диплом бакалавра  АА 000000; 01.01.2020; Ким видано: Якийсь університет</t>
-  </si>
-  <si>
-    <t>Савченко Юлія Андріївна</t>
-  </si>
-  <si>
-    <t>Диплом бакалавра  PL 556677; 15.07.2023; Ким видано: Університет Варшави, Польща</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,13 +121,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,6 +158,12 @@
         <fgColor rgb="FFFFD7D7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7FFD7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -135,19 +177,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFD7FFD7"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -444,92 +493,121 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="108.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/static/templates/import_education_docs.xlsx
+++ b/static/templates/import_education_docs.xlsx
@@ -1,144 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LocalAdm\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59902412-BC9E-46C2-AE78-4576BCE67D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="345" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Документи" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Документи" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>Коваленко Марія Петрівна</t>
-  </si>
-  <si>
-    <t>Атестат про повну загальну середню освіту  БК 40920464; 15.06.2021; Ким видано: Ліцей №5 м. Одеса</t>
-  </si>
-  <si>
-    <t>Бондаренко Олег Васильович</t>
-  </si>
-  <si>
-    <t>Диплом молодшого спеціаліста  КМ 12345678; 30.06.2022; Ким видано: Київський коледж будівництва</t>
-  </si>
-  <si>
-    <t>Мельник Оксана Миколаївна</t>
-  </si>
-  <si>
-    <t>Диплом бакалавра  ВО 99887766; 25.06.2023; Ким видано: Львівський національний університет імені Івана Франка</t>
-  </si>
-  <si>
-    <t>Ткаченко Василь Іванович</t>
-  </si>
-  <si>
-    <t>Диплом бакалавра B24 001122; 10.06.2024; Харківський університет</t>
-  </si>
-  <si>
-    <t>Петренко Анна Сергіївна</t>
-  </si>
-  <si>
-    <t>Атестат НА 123456 20.06.2021 Ким видано: Школа №10</t>
-  </si>
-  <si>
-    <t>Іваненко Дмитро Олегович</t>
-  </si>
-  <si>
-    <t>Неіснуючий Студент Повністю</t>
-  </si>
-  <si>
-    <t>Диплом бакалавра  АА 000000; 01.01.2020; Ким видано: Якийсь університет</t>
-  </si>
-  <si>
-    <t>Савченко Юлія Андріївна</t>
-  </si>
-  <si>
-    <t>Диплом бакалавра  PL 556677; 15.07.2023; Ким видано: Університет Варшави, Польща</t>
-  </si>
-  <si>
-    <t>Мельник Денис Богданович</t>
-  </si>
-  <si>
-    <t>ПІБ студента</t>
-  </si>
-  <si>
-    <t>Рядок документа</t>
-  </si>
-  <si>
-    <t>Академічна довідка (укр)</t>
-  </si>
-  <si>
-    <t>Академічна довідка (en)</t>
-  </si>
-  <si>
-    <t>Свідоцтво про визнання (укр)</t>
-  </si>
-  <si>
-    <t>Свідоцтво про визнання (en)</t>
-  </si>
-  <si>
-    <t>№ N-7916-20; Private HEI "European University"; 12.05.2020</t>
-  </si>
-  <si>
-    <t>08-17/04; ТОВ Кавказький університет; Грузія; 02/06/2017</t>
-  </si>
-  <si>
-    <t>08-17/04; Caucasus University LLC; Georgia; 02/06/2017</t>
-  </si>
-  <si>
-    <t>№ N-7916-20; Приватний ВНЗ «Європейський університет»; 12/05/2020</t>
-  </si>
-  <si>
-    <t>Диплом бакалавра  B24 088726; 20.06.2024; Ким видано: Харківський національний університет імені В.Н. Каразіна</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -158,12 +56,6 @@
         <fgColor rgb="FFFFD7D7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7FFD7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -177,34 +69,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
-    <mruColors>
-      <color rgb="FFD7FFD7"/>
-    </mruColors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -492,122 +434,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="108.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="60.7109375" bestFit="1" customWidth="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ПІБ студента</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Рядок документа</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Академічна довідка</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Свідоцтво про визнання</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Мельник Денис Богданович</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра  B24 088726; 20.06.2024; Ким видано: Харківський національний університет імені В.Н. Каразіна</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>08-17/04; ТОВ Кавказький університет; Грузія; 02.06.2017</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>№ N-7916-20; Приватний ВНЗ «Європейський університет»; 12.05.2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Коваленко Марія Петрівна</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Атестат про повну загальну середню освіту  БК 40920464; 15.06.2021; Ким видано: Ліцей №5 м. Одеса</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Бондаренко Олег Васильович</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Диплом молодшого спеціаліста  КМ 12345678; 30.06.2022; Ким видано: Київський коледж будівництва</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Мельник Оксана Миколаївна</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра  ВО 99887766; 25.06.2023; Ким видано: Львівський національний університет імені Івана Франка</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Ткаченко Василь Іванович</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра B24 001122; 10.06.2024; Харківський університет</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Петренко Анна Сергіївна</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Атестат НА 123456 20.06.2021 Ким видано: Школа №10</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Іваненко Дмитро Олегович</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Неіснуючий Студент Повністю</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра  АА 000000; 01.01.2020; Ким видано: Якийсь університет</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Савченко Юлія Андріївна</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра  PL 556677; 15.07.2023; Ким видано: Університет Варшави, Польща</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>